--- a/data/trans_dic/IP18A05-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas</t>
+          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,39</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,84</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,49</t>
+          <t>0,0; 12,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 4,73</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,75</t>
+          <t>0,0; 7,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,88</t>
+          <t>0,0; 15,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,2</t>
+          <t>0,0; 2,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 10,5</t>
+          <t>0,89; 10,57</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,71</t>
+          <t>0,0; 7,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 3,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,1</t>
+          <t>0,0; 5,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,2</t>
+          <t>0,0; 5,31</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,61</t>
+          <t>0,0; 40,95</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,57</t>
+          <t>0,31; 3,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,09</t>
+          <t>0,28; 2,8</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,54</t>
+          <t>0,0; 26,02</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,87</t>
+          <t>0,0; 6,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,17</t>
+          <t>0,34; 3,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,3</t>
+          <t>0,29; 3,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,77; 17,1</t>
+          <t>1,9; 17,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,15</t>
+          <t>0,34; 3,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,82</t>
+          <t>0,5; 4,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,85</t>
+          <t>0,0; 7,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,89</t>
+          <t>0,2; 1,82</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 2,63</t>
+          <t>0,57; 2,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 3,29</t>
+          <t>0,71; 2,99</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 9,97</t>
+          <t>1,43; 9,02</t>
         </is>
       </c>
     </row>
@@ -1276,42 +1277,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,66</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 4,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 3,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 4,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,17 +1322,17 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 1,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,03</t>
+          <t>0,0; 1,97</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,88</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,58</t>
+          <t>0,0; 8,57</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 8,5</t>
+          <t>1,06; 9,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,9</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 6,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,95</t>
+          <t>0,0; 6,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,01</t>
+          <t>0,0; 47,14</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,17</t>
+          <t>0,0; 3,75</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,27</t>
+          <t>1,06; 6,04</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,67</t>
+          <t>0,0; 27,45</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,34</t>
+          <t>0,14; 1,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,55</t>
+          <t>0,32; 1,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,84</t>
+          <t>0,4; 1,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,43</t>
+          <t>1,05; 6,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,35</t>
+          <t>0,2; 1,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,09</t>
+          <t>0,54; 2,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,45</t>
+          <t>0,7; 2,39</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,55; 8,73</t>
+          <t>1,4; 8,45</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,01</t>
+          <t>0,3; 1,17</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,54</t>
+          <t>0,58; 1,53</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,77</t>
+          <t>0,7; 1,77</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 6,35</t>
+          <t>1,72; 6,08</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>707</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>793</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>1463</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1727</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1622</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3571</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4865</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3302</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3163</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4059</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6909</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3174</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3984</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5305</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6457</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>403; 4790</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1602</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1661</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1514</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2086</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2205</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>1514</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5634</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2480</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2924</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4972</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5238</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6633</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>483; 6057</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5330</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>549; 5459</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6944</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1481</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1481</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5199</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4478</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>711</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2671</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1981</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1646</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3410</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1001</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2357</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>5555</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5830</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2982</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3590</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>652; 6728</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>604; 7106</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>572; 5293</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 6028</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>742; 7164</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>933; 8773</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3168</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>686; 6351</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2307; 10230</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2802; 11778</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>1017; 6435</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3327</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4862</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3237</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4680</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4867</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4951</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4937</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1876</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3226</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4513</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>599; 5107</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4174</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4186</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5502</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4576</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>1244; 7086</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5771</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>3106</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4956</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>5486</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2896</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>8824</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5143</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>6631</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>12833</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>14310</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>8039</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>794; 7924</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>2013; 9282</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2466; 10579</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1035; 6687</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1183; 8191</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3653; 13590</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>4442; 15216</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>1824; 11015</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>3480; 13447</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>7641; 19972</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>8710; 22026</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>3950; 13934</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP18A05-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Clase-trans_dic.xlsx
@@ -717,22 +717,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>0,0; 4,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,38</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,77</t>
+          <t>0,0; 11,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -742,37 +742,37 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,73</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 5,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,45</t>
+          <t>0,0; 15,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,21</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,89; 10,57</t>
+          <t>0,94; 9,48</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,02</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 3,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,42 +877,42 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,88</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,68</t>
+          <t>0,0; 5,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,31</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,95</t>
+          <t>0,0; 34,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,89</t>
+          <t>0,31; 4,05</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,8</t>
+          <t>0,28; 3,22</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,02</t>
+          <t>0,0; 27,62</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,26</t>
+          <t>0,0; 6,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,51</t>
+          <t>0,35; 3,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,46</t>
+          <t>0,32; 3,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,9; 17,52</t>
+          <t>1,76; 17,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,32</t>
+          <t>0,34; 3,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,66</t>
+          <t>0,58; 4,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,7</t>
+          <t>0,0; 8,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,82</t>
+          <t>0,2; 2,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,51</t>
+          <t>0,65; 2,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,99</t>
+          <t>0,6; 3,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 9,02</t>
+          <t>1,16; 8,84</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 3,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,73</t>
+          <t>0,0; 4,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>0,0; 2,14</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,67</t>
+          <t>0,0; 3,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,97</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,57</t>
+          <t>0,0; 7,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,07</t>
+          <t>1,06; 8,88</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,01</t>
+          <t>0,0; 5,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,87</t>
+          <t>0,0; 6,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,14</t>
+          <t>0,0; 47,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,0; 4,73</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,04</t>
+          <t>1,07; 6,18</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,45</t>
+          <t>0,0; 27,91</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,41</t>
+          <t>0,14; 1,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,47</t>
+          <t>0,33; 1,55</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,74</t>
+          <t>0,42; 1,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 6,78</t>
+          <t>1,06; 6,79</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,38</t>
+          <t>0,23; 1,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,02</t>
+          <t>0,56; 1,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,39</t>
+          <t>0,69; 2,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 8,45</t>
+          <t>1,53; 7,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 1,17</t>
+          <t>0,29; 1,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,53</t>
+          <t>0,58; 1,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 1,77</t>
+          <t>0,67; 1,78</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,08</t>
+          <t>1,9; 6,72</t>
         </is>
       </c>
     </row>
@@ -1927,22 +1927,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3571</t>
+          <t>0; 3232</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4865</t>
+          <t>0; 3865</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3302</t>
+          <t>0; 3308</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3163</t>
+          <t>0; 2738</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1952,37 +1952,37 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4059</t>
+          <t>0; 3655</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 6909</t>
+          <t>0; 4967</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3174</t>
+          <t>0; 3212</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3984</t>
+          <t>0; 3940</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 5305</t>
+          <t>0; 4493</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6457</t>
+          <t>0; 6255</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>403; 4790</t>
+          <t>426; 4297</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5634</t>
+          <t>0; 4916</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2480</t>
+          <t>0; 2973</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2155,42 +2155,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2924</t>
+          <t>0; 2442</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4972</t>
+          <t>0; 5211</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5238</t>
+          <t>0; 5469</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 6633</t>
+          <t>0; 5640</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>483; 6057</t>
+          <t>481; 6309</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5330</t>
+          <t>0; 5093</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>549; 5459</t>
+          <t>553; 6285</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 6944</t>
+          <t>0; 7371</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5199</t>
+          <t>0; 5108</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 4478</t>
+          <t>0; 5068</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3590</t>
+          <t>0; 4046</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>652; 6728</t>
+          <t>665; 7176</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>604; 7106</t>
+          <t>650; 7222</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>572; 5293</t>
+          <t>531; 5352</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6028</t>
+          <t>0; 5631</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>742; 7164</t>
+          <t>742; 7124</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>933; 8773</t>
+          <t>1086; 8271</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3168</t>
+          <t>0; 3377</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>686; 6351</t>
+          <t>686; 7044</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2307; 10230</t>
+          <t>2645; 10343</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2802; 11778</t>
+          <t>2354; 12139</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1017; 6435</t>
+          <t>826; 6307</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3327</t>
+          <t>0; 4343</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4862</t>
+          <t>0; 4870</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3237</t>
+          <t>0; 2833</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4680</t>
+          <t>0; 4782</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2799,17 +2799,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4867</t>
+          <t>0; 5279</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 4951</t>
+          <t>0; 4983</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4937</t>
+          <t>0; 4586</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4513</t>
+          <t>0; 3898</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>599; 5107</t>
+          <t>596; 5001</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4174</t>
+          <t>0; 3539</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4186</t>
+          <t>0; 4179</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5502</t>
+          <t>0; 5507</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4576</t>
+          <t>0; 5777</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1244; 7086</t>
+          <t>1258; 7243</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 5771</t>
+          <t>0; 5870</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>794; 7924</t>
+          <t>794; 7758</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2013; 9282</t>
+          <t>2108; 9795</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2466; 10579</t>
+          <t>2535; 10658</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1035; 6687</t>
+          <t>1041; 6697</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1183; 8191</t>
+          <t>1383; 8268</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3653; 13590</t>
+          <t>3805; 13142</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4442; 15216</t>
+          <t>4390; 14898</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1824; 11015</t>
+          <t>1999; 10422</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3480; 13447</t>
+          <t>3319; 12394</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7641; 19972</t>
+          <t>7638; 18959</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8710; 22026</t>
+          <t>8328; 22209</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3950; 13934</t>
+          <t>4351; 15388</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP18A05-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP18A05-Clase-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,86%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,74</t>
+          <t>0,0; 4,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,75</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 16,35</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 4,39</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 11,05</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,26</t>
+          <t>0,0; 4,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,34</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,64</t>
+          <t>0,0; 13,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,2</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 4,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 9,48</t>
+          <t>0,85; 10,31</t>
         </is>
       </c>
     </row>
@@ -789,44 +789,44 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1,34%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,17%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,12</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,08</t>
+          <t>0,0; 5,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 41,89</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 6,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,82</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,05</t>
+          <t>0,31; 3,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,22</t>
+          <t>0,28; 3,09</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,62</t>
+          <t>0,0; 24,67</t>
         </is>
       </c>
     </row>
@@ -934,27 +934,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 5,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,1</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,18%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6,56%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,74</t>
+          <t>0,34; 3,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,51</t>
+          <t>0,5; 4,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 17,72</t>
+          <t>0,0; 7,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,3</t>
+          <t>0,36; 3,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 4,39</t>
+          <t>0,29; 3,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,21</t>
+          <t>1,64; 17,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,02</t>
+          <t>0,2; 1,89</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,54</t>
+          <t>0,66; 2,63</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,08</t>
+          <t>0,62; 3,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 8,84</t>
+          <t>1,53; 10,56</t>
         </is>
       </c>
     </row>
@@ -1209,37 +1209,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,53%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,17</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,14</t>
+          <t>0,0; 2,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,83</t>
+          <t>0,0; 2,03</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1354,44 +1354,44 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>18,23%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>1,46%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3,33%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>16,46%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>1,19%</t>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -1422,17 +1422,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,4</t>
+          <t>0,0; 4,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 8,88</t>
+          <t>0,0; 6,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 50,88</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,17 +1442,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,09</t>
+          <t>0,0; 7,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,86</t>
+          <t>1,07; 8,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,73</t>
+          <t>0,0; 4,17</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 6,18</t>
+          <t>1,07; 6,27</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,91</t>
+          <t>0,0; 30,4</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>4,11%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>0,55%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0,9%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,38</t>
+          <t>0,23; 1,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>0,64; 2,09</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0,74; 2,45</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1,59; 9,65</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,14; 1,34</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>0,33; 1,55</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0,42; 1,75</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1,06; 6,79</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0,23; 1,4</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,56; 1,95</t>
-        </is>
-      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,34</t>
+          <t>0,41; 1,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 7,99</t>
+          <t>1,09; 7,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,07</t>
+          <t>0,27; 1,01</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,45</t>
+          <t>0,61; 1,54</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,78</t>
+          <t>0,69; 1,77</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,72</t>
+          <t>1,89; 6,61</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
+          <t>Menores cuya última consulta médica fue por dispensación de recetas (tasa de respuesta: 98,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>673</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1081</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>793</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>790</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>915</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1081</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>828</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>1444</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3232</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3865</t>
+          <t>0; 3764</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3308</t>
+          <t>0; 5343</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2738</t>
+          <t>0; 3091</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4149</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3655</t>
+          <t>0; 3947</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4967</t>
+          <t>0; 3732</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3212</t>
+          <t>0; 2856</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3940</t>
+          <t>0; 3971</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 4493</t>
+          <t>0; 4756</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 6255</t>
+          <t>0; 7627</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>426; 4297</t>
+          <t>343; 4186</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,54 +2067,54 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1661</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1602</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>544</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2086</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>1500</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1661</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1514</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2086</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1500</t>
-        </is>
-      </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
           <t>2205</t>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1605</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4916</t>
+          <t>0; 3074</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5337</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2973</t>
+          <t>0; 5123</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 6610</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2442</t>
+          <t>0; 5385</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 5211</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 5469</t>
+          <t>0; 2761</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 5640</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>481; 6309</t>
+          <t>479; 5550</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5093</t>
+          <t>0; 5408</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>553; 6285</t>
+          <t>549; 6019</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 7371</t>
+          <t>0; 6412</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1481</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1481</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4872</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5108</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 5068</t>
+          <t>0; 5157</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1646</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2884</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3410</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>711</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2671</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>2421</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1646</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2884</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3410</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2735</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4046</t>
+          <t>0; 5358</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>665; 7176</t>
+          <t>742; 6784</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>650; 7222</t>
+          <t>939; 9088</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>531; 5352</t>
+          <t>0; 2716</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5631</t>
+          <t>0; 3573</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>742; 7124</t>
+          <t>683; 6079</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1086; 8271</t>
+          <t>601; 6787</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3377</t>
+          <t>481; 5077</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>686; 7044</t>
+          <t>688; 6583</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2645; 10343</t>
+          <t>2675; 10700</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2354; 12139</t>
+          <t>2451; 12947</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>826; 6307</t>
+          <t>1031; 7122</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2691,37 +2691,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1395</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1322</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>726</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1395</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
-        </is>
-      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2759,17 +2759,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4229</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 4343</t>
+          <t>0; 3732</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4619</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2779,17 +2779,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4870</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 2833</t>
+          <t>0; 3642</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4782</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2799,17 +2799,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5279</t>
+          <t>0; 4862</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0; 4983</t>
+          <t>0; 5534</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4586</t>
+          <t>0; 5080</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2904,37 +2904,37 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1912</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>769</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1876</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1351</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1912</t>
         </is>
       </c>
     </row>
@@ -2972,17 +2972,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3898</t>
+          <t>0; 3408</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>596; 5001</t>
+          <t>0; 4235</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5338</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 3539</t>
+          <t>0; 3993</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 4179</t>
+          <t>600; 4785</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 5507</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3012,17 +3012,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 5777</t>
+          <t>0; 5092</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1258; 7243</t>
+          <t>1254; 7351</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 5870</t>
+          <t>0; 6104</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3525</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>7877</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>8824</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>4954</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>3106</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>4956</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>5486</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2896</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>3525</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>7877</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>8824</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5143</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>7697</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>794; 7758</t>
+          <t>1382; 8026</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2108; 9795</t>
+          <t>4310; 14081</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2535; 10658</t>
+          <t>4677; 15596</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1041; 6697</t>
+          <t>1922; 11644</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1383; 8268</t>
+          <t>769; 7516</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3805; 13142</t>
+          <t>2084; 9802</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4390; 14898</t>
+          <t>2486; 11223</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1999; 10422</t>
+          <t>1024; 7050</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3319; 12394</t>
+          <t>3153; 11687</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7638; 18959</t>
+          <t>7994; 20067</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8328; 22209</t>
+          <t>8550; 22027</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4351; 15388</t>
+          <t>4047; 14184</t>
         </is>
       </c>
     </row>
